--- a/predictions/SES.xlsx
+++ b/predictions/SES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,21 @@
           <t>ape</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>custom_ape</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>group_wape</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>wape</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +504,15 @@
       <c r="H2" t="n">
         <v>7.519</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,6 +545,15 @@
       <c r="H3" t="n">
         <v>0.966</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,6 +586,15 @@
       <c r="H4" t="n">
         <v>0.615</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,6 +625,15 @@
         <v>0.017</v>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -613,6 +664,15 @@
         <v>2.678</v>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>14.661</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.222</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -643,6 +703,15 @@
         <v>2.639</v>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,6 +742,15 @@
         <v>0.01</v>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -705,6 +783,15 @@
       <c r="H9" t="n">
         <v>3.309</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,6 +822,15 @@
         <v>2.573</v>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -765,6 +861,15 @@
         <v>8.895</v>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -797,6 +902,15 @@
       <c r="H12" t="n">
         <v>0.772</v>
       </c>
+      <c r="I12" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -827,6 +941,15 @@
         <v>1.968</v>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>12.566</v>
+      </c>
+      <c r="J13" t="n">
+        <v>37.222</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +980,15 @@
         <v>1.939</v>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -889,6 +1021,15 @@
       <c r="H15" t="n">
         <v>0.614</v>
       </c>
+      <c r="I15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -921,6 +1062,15 @@
       <c r="H16" t="n">
         <v>0.316</v>
       </c>
+      <c r="I16" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -953,6 +1103,15 @@
       <c r="H17" t="n">
         <v>14.258</v>
       </c>
+      <c r="I17" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -985,6 +1144,15 @@
       <c r="H18" t="n">
         <v>0.911</v>
       </c>
+      <c r="I18" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1017,6 +1185,15 @@
       <c r="H19" t="n">
         <v>0.838</v>
       </c>
+      <c r="I19" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1049,6 +1226,15 @@
       <c r="H20" t="n">
         <v>9.994999999999999</v>
       </c>
+      <c r="I20" t="n">
+        <v>9.994999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>37.222</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1081,6 +1267,15 @@
       <c r="H21" t="n">
         <v>0.228</v>
       </c>
+      <c r="I21" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.994</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1112,6 +1307,15 @@
       </c>
       <c r="H22" t="n">
         <v>0.9350000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.994</v>
       </c>
     </row>
   </sheetData>
